--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_3_1.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/pbc/PbcReport_3_1.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="14805" windowHeight="7980"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14355" windowHeight="4920"/>
   </bookViews>
   <sheets>
     <sheet name="表3-1存续产品分期限募集余额" sheetId="4" r:id="rId1"/>
@@ -16,7 +16,7 @@
     <definedName name="Err">[1]综合校验!$B$2</definedName>
     <definedName name="Thd">[1]综合校验!$B$1</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -48,6 +48,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -66,6 +67,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -84,6 +86,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -102,6 +105,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -120,6 +124,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -138,6 +143,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -156,6 +162,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -313,9 +320,6 @@
     <t>列编号</t>
   </si>
   <si>
-    <t>单位：万元</t>
-  </si>
-  <si>
     <t>产品品种：</t>
   </si>
   <si>
@@ -555,6 +559,10 @@
   </si>
   <si>
     <t>${AMT_e00000_CXCPMJYEZJ.cny}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：万元</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -566,9 +574,9 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="178" formatCode="##0.00"/>
-    <numFmt numFmtId="180" formatCode="#,##0.000000_ "/>
+    <numFmt numFmtId="179" formatCode="#,##0.000000_ "/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,21 +587,25 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -611,6 +623,7 @@
       <b/>
       <sz val="12"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -641,7 +654,16 @@
       <b/>
       <sz val="16"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -823,7 +845,7 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -906,6 +928,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1000,7 +1025,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1042,7 +1067,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1077,7 +1102,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1301,7 +1326,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="21" customFormat="1" ht="24.95" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -1315,48 +1340,48 @@
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F2" s="23"/>
       <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:7" s="21" customFormat="1" ht="24.95" customHeight="1">
       <c r="A3" s="24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="42"/>
       <c r="D3" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="20" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
       <c r="A4" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="38"/>
       <c r="E4" s="39"/>
       <c r="F4" s="39"/>
       <c r="G4" s="37" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="20" customFormat="1" ht="15.95" customHeight="1">
@@ -1405,13 +1430,13 @@
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
       <c r="E7" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F7" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="26" t="s">
         <v>142</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.95" customHeight="1">
@@ -1426,13 +1451,13 @@
         <v>53</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.95" customHeight="1">
@@ -1536,13 +1561,13 @@
         <v>4</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.95" customHeight="1">
@@ -1557,13 +1582,13 @@
         <v>42</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.95" customHeight="1">
@@ -1667,13 +1692,13 @@
         <v>4</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G25" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1688,13 +1713,13 @@
         <v>31</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1707,13 +1732,13 @@
         <v>18</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1726,13 +1751,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1745,13 +1770,13 @@
         <v>14</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G29" s="26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1764,13 +1789,13 @@
         <v>12</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1783,13 +1808,13 @@
         <v>10</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G31" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1802,13 +1827,13 @@
         <v>8</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G32" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1821,13 +1846,13 @@
         <v>6</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G33" s="26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:7" s="6" customFormat="1" ht="15.95" customHeight="1">
@@ -1855,13 +1880,13 @@
         <v>20</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.95" customHeight="1">
@@ -1874,13 +1899,13 @@
         <v>18</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G36" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.95" customHeight="1">
@@ -1893,13 +1918,13 @@
         <v>16</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G37" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.95" customHeight="1">
@@ -1912,13 +1937,13 @@
         <v>14</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G38" s="26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.95" customHeight="1">
@@ -1931,13 +1956,13 @@
         <v>12</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G39" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.95" customHeight="1">
@@ -1950,13 +1975,13 @@
         <v>10</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G40" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.95" customHeight="1">
@@ -1969,13 +1994,13 @@
         <v>8</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G41" s="26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.95" customHeight="1">
@@ -1988,13 +2013,13 @@
         <v>6</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G42" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.95" customHeight="1" thickBot="1">
@@ -2026,20 +2051,20 @@
         <v>2</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="11" t="s">
         <v>1</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>0</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2055,12 +2080,12 @@
     <mergeCell ref="B35:C43"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:C16"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B8:C16"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
